--- a/Result/25-04-25/NASDAQstock_25-04-25period252RS90.xlsx
+++ b/Result/25-04-25/NASDAQstock_25-04-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/25-04-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBD6087-4FCB-844F-9A14-7ED7FDA8FDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC235CA-0A1C-4544-92E1-98B3A291FD81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -834,7 +834,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -11489,7 +11488,7 @@
       </c>
     </row>
     <row r="84" spans="1:42">
-      <c r="A84" s="9" t="s">
+      <c r="A84" t="s">
         <v>219</v>
       </c>
       <c r="B84">
